--- a/Tabla_Nvasosnuevos.xlsx
+++ b/Tabla_Nvasosnuevos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\Qca_Bruto\Minicores-Q.canariensis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CCF7FE-F152-482F-984B-032F6411E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41092F9C-7644-498C-ACDE-0C9322140032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="newvess" sheetId="1" r:id="rId1"/>
@@ -30622,7 +30622,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>76000</v>
+        <v>760000</v>
       </c>
       <c r="C2" s="10">
         <v>44329</v>
@@ -30633,7 +30633,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16000</v>
+        <v>160000</v>
       </c>
       <c r="C3" s="10">
         <v>44343</v>
@@ -30644,7 +30644,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>73000</v>
+        <v>730000</v>
       </c>
       <c r="C4" s="10">
         <v>44399</v>
@@ -30655,7 +30655,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>132000</v>
+        <v>1320000</v>
       </c>
       <c r="C5" s="10">
         <v>44448</v>
@@ -30666,7 +30666,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>274900</v>
+        <v>2749000</v>
       </c>
       <c r="C6" s="10">
         <v>44483</v>
@@ -30677,7 +30677,7 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>20090</v>
+        <v>200900</v>
       </c>
       <c r="C7" s="10">
         <v>44546</v>
@@ -30688,7 +30688,7 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>5640</v>
+        <v>56400</v>
       </c>
       <c r="C8" s="10">
         <v>44215</v>
@@ -30699,7 +30699,7 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <v>287000</v>
+        <v>2870000</v>
       </c>
       <c r="C9" s="10">
         <v>44287</v>
@@ -30710,7 +30710,7 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>91039</v>
+        <v>910390</v>
       </c>
       <c r="C10" s="10">
         <v>44315</v>
@@ -30721,7 +30721,7 @@
         <v>3</v>
       </c>
       <c r="B11">
-        <v>101039</v>
+        <v>1010390</v>
       </c>
       <c r="C11" s="10">
         <v>44329</v>

--- a/Tabla_Nvasosnuevos.xlsx
+++ b/Tabla_Nvasosnuevos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\Qca_Bruto\Minicores-Q.canariensis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41092F9C-7644-498C-ACDE-0C9322140032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F210CE60-DF6F-4166-A691-2275F0FB8207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="newvess" sheetId="1" r:id="rId1"/>
@@ -1519,7 +1519,7 @@
         <v>2</v>
       </c>
       <c r="L27" s="4">
-        <v>44542</v>
+        <v>44546</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
         <v>2</v>
       </c>
       <c r="L28" s="4">
-        <v>44542</v>
+        <v>44546</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1595,7 +1595,7 @@
         <v>2</v>
       </c>
       <c r="L29" s="4">
-        <v>44542</v>
+        <v>44546</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -1633,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="L30" s="4">
-        <v>44542</v>
+        <v>44546</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
         <v>2</v>
       </c>
       <c r="L31" s="4">
-        <v>44542</v>
+        <v>44546</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1709,7 +1709,7 @@
         <v>2</v>
       </c>
       <c r="L32" s="4">
-        <v>44542</v>
+        <v>44546</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -6193,7 +6193,7 @@
         <v>5</v>
       </c>
       <c r="L150" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6231,7 +6231,7 @@
         <v>5</v>
       </c>
       <c r="L151" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6269,7 +6269,7 @@
         <v>5</v>
       </c>
       <c r="L152" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6307,7 +6307,7 @@
         <v>5</v>
       </c>
       <c r="L153" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6345,7 +6345,7 @@
         <v>5</v>
       </c>
       <c r="L154" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6383,7 +6383,7 @@
         <v>5</v>
       </c>
       <c r="L155" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6421,7 +6421,7 @@
         <v>5</v>
       </c>
       <c r="L156" s="11">
-        <v>44490</v>
+        <v>44483</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6611,7 +6611,7 @@
         <v>8</v>
       </c>
       <c r="L161" s="11">
-        <v>44287</v>
+        <v>44315</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6649,7 +6649,7 @@
         <v>8</v>
       </c>
       <c r="L162" s="11">
-        <v>44287</v>
+        <v>44315</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6687,7 +6687,7 @@
         <v>8</v>
       </c>
       <c r="L163" s="11">
-        <v>44287</v>
+        <v>44315</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -30625,7 +30625,7 @@
         <v>760000</v>
       </c>
       <c r="C2" s="10">
-        <v>44329</v>
+        <v>44301</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -30636,7 +30636,7 @@
         <v>160000</v>
       </c>
       <c r="C3" s="10">
-        <v>44343</v>
+        <v>44329</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -30691,7 +30691,7 @@
         <v>56400</v>
       </c>
       <c r="C8" s="10">
-        <v>44215</v>
+        <v>44580</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -30699,7 +30699,7 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <v>2870000</v>
+        <v>287000</v>
       </c>
       <c r="C9" s="10">
         <v>44287</v>
@@ -30779,7 +30779,7 @@
         <v>96112.072</v>
       </c>
       <c r="C16" s="10">
-        <v>44571</v>
+        <v>44580</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">

--- a/Tabla_Nvasosnuevos.xlsx
+++ b/Tabla_Nvasosnuevos.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\minicores\Qca_Bruto\Minicores-Q.canariensis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F210CE60-DF6F-4166-A691-2275F0FB8207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E19223-8739-41F1-B2B2-7AD5FD97C78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="newvess" sheetId="1" r:id="rId1"/>
     <sheet name="newarea" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">newvess!$A$1:$L$792</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -483,6 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M792"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -491,7 +495,7 @@
     <col min="6" max="6" width="15.7109375" style="9" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="35.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -533,7 +537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -572,7 +576,7 @@
       </c>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -610,7 +614,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -648,7 +652,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -686,7 +690,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -724,7 +728,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -762,7 +766,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -800,7 +804,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -838,7 +842,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -876,7 +880,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>4</v>
       </c>
@@ -914,7 +918,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>5</v>
       </c>
@@ -952,7 +956,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>6</v>
       </c>
@@ -990,7 +994,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>7</v>
       </c>
@@ -1028,7 +1032,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>8</v>
       </c>
@@ -1066,7 +1070,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>9</v>
       </c>
@@ -1104,7 +1108,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>10</v>
       </c>
@@ -1142,7 +1146,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>11</v>
       </c>
@@ -1180,7 +1184,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>12</v>
       </c>
@@ -1218,7 +1222,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>13</v>
       </c>
@@ -1256,7 +1260,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1</v>
       </c>
@@ -1294,7 +1298,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2</v>
       </c>
@@ -1332,7 +1336,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>3</v>
       </c>
@@ -1370,7 +1374,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>4</v>
       </c>
@@ -1408,7 +1412,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>5</v>
       </c>
@@ -1446,7 +1450,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>6</v>
       </c>
@@ -1484,7 +1488,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>1</v>
       </c>
@@ -1522,7 +1526,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2</v>
       </c>
@@ -1560,7 +1564,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>3</v>
       </c>
@@ -1598,7 +1602,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>4</v>
       </c>
@@ -1636,7 +1640,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>5</v>
       </c>
@@ -1674,7 +1678,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>6</v>
       </c>
@@ -1712,7 +1716,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>1</v>
       </c>
@@ -1750,7 +1754,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2</v>
       </c>
@@ -1788,7 +1792,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>3</v>
       </c>
@@ -1826,7 +1830,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>4</v>
       </c>
@@ -1864,7 +1868,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>5</v>
       </c>
@@ -1902,7 +1906,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>6</v>
       </c>
@@ -1940,7 +1944,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>7</v>
       </c>
@@ -1978,7 +1982,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>8</v>
       </c>
@@ -2016,7 +2020,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1</v>
       </c>
@@ -2054,7 +2058,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2</v>
       </c>
@@ -2092,7 +2096,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1</v>
       </c>
@@ -2130,7 +2134,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1</v>
       </c>
@@ -2168,7 +2172,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2</v>
       </c>
@@ -2206,7 +2210,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>3</v>
       </c>
@@ -2244,7 +2248,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4</v>
       </c>
@@ -2282,7 +2286,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5</v>
       </c>
@@ -2320,7 +2324,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>6</v>
       </c>
@@ -2358,7 +2362,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>7</v>
       </c>
@@ -2396,7 +2400,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>8</v>
       </c>
@@ -2434,7 +2438,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9</v>
       </c>
@@ -2472,7 +2476,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>10</v>
       </c>
@@ -2510,7 +2514,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>11</v>
       </c>
@@ -2548,7 +2552,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1</v>
       </c>
@@ -2586,7 +2590,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2</v>
       </c>
@@ -2624,7 +2628,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>3</v>
       </c>
@@ -2662,7 +2666,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>4</v>
       </c>
@@ -2700,7 +2704,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>5</v>
       </c>
@@ -2738,7 +2742,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>6</v>
       </c>
@@ -2776,7 +2780,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>7</v>
       </c>
@@ -2814,7 +2818,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>8</v>
       </c>
@@ -2852,7 +2856,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>9</v>
       </c>
@@ -2890,7 +2894,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>10</v>
       </c>
@@ -2928,7 +2932,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>11</v>
       </c>
@@ -2966,7 +2970,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>12</v>
       </c>
@@ -3004,7 +3008,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1</v>
       </c>
@@ -3042,7 +3046,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2</v>
       </c>
@@ -3080,7 +3084,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>3</v>
       </c>
@@ -3118,7 +3122,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>4</v>
       </c>
@@ -3156,7 +3160,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>5</v>
       </c>
@@ -3194,7 +3198,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>6</v>
       </c>
@@ -3232,7 +3236,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>7</v>
       </c>
@@ -3270,7 +3274,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>8</v>
       </c>
@@ -3308,7 +3312,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>9</v>
       </c>
@@ -3346,7 +3350,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>10</v>
       </c>
@@ -3384,7 +3388,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>11</v>
       </c>
@@ -3422,7 +3426,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>12</v>
       </c>
@@ -3460,7 +3464,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>13</v>
       </c>
@@ -3498,7 +3502,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>14</v>
       </c>
@@ -3536,7 +3540,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>15</v>
       </c>
@@ -3574,7 +3578,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>16</v>
       </c>
@@ -3612,7 +3616,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>17</v>
       </c>
@@ -3650,7 +3654,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>18</v>
       </c>
@@ -3688,7 +3692,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>19</v>
       </c>
@@ -3726,7 +3730,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>20</v>
       </c>
@@ -3764,7 +3768,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>21</v>
       </c>
@@ -3802,7 +3806,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>22</v>
       </c>
@@ -3840,7 +3844,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>23</v>
       </c>
@@ -3878,7 +3882,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>24</v>
       </c>
@@ -3916,7 +3920,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>25</v>
       </c>
@@ -3954,7 +3958,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>26</v>
       </c>
@@ -3992,7 +3996,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1</v>
       </c>
@@ -4030,7 +4034,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2</v>
       </c>
@@ -4068,7 +4072,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>3</v>
       </c>
@@ -4106,7 +4110,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>4</v>
       </c>
@@ -4144,7 +4148,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>5</v>
       </c>
@@ -4182,7 +4186,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>6</v>
       </c>
@@ -4220,7 +4224,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>7</v>
       </c>
@@ -4258,7 +4262,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>8</v>
       </c>
@@ -4296,7 +4300,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>9</v>
       </c>
@@ -4334,7 +4338,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>10</v>
       </c>
@@ -4372,7 +4376,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>11</v>
       </c>
@@ -4410,7 +4414,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>12</v>
       </c>
@@ -4448,7 +4452,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>13</v>
       </c>
@@ -4486,7 +4490,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>14</v>
       </c>
@@ -4524,7 +4528,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>15</v>
       </c>
@@ -4562,7 +4566,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>16</v>
       </c>
@@ -4600,7 +4604,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>17</v>
       </c>
@@ -4638,7 +4642,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>18</v>
       </c>
@@ -4676,7 +4680,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>19</v>
       </c>
@@ -4714,7 +4718,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1</v>
       </c>
@@ -4752,7 +4756,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2</v>
       </c>
@@ -4790,7 +4794,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>3</v>
       </c>
@@ -4828,7 +4832,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>4</v>
       </c>
@@ -4866,7 +4870,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>5</v>
       </c>
@@ -4904,7 +4908,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>6</v>
       </c>
@@ -4942,7 +4946,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>7</v>
       </c>
@@ -4980,7 +4984,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>8</v>
       </c>
@@ -5018,7 +5022,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>9</v>
       </c>
@@ -5056,7 +5060,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>10</v>
       </c>
@@ -5094,7 +5098,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>11</v>
       </c>
@@ -5132,7 +5136,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>12</v>
       </c>
@@ -5170,7 +5174,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12">
         <v>1</v>
       </c>
@@ -5208,7 +5212,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12">
         <v>2</v>
       </c>
@@ -5246,7 +5250,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12">
         <v>1</v>
       </c>
@@ -5284,7 +5288,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12">
         <v>2</v>
       </c>
@@ -5322,7 +5326,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12">
         <v>1</v>
       </c>
@@ -5360,7 +5364,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12">
         <v>1</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12">
         <v>2</v>
       </c>
@@ -5436,7 +5440,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12">
         <v>1</v>
       </c>
@@ -5474,7 +5478,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12">
         <v>2</v>
       </c>
@@ -5512,7 +5516,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12">
         <v>3</v>
       </c>
@@ -5550,7 +5554,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12">
         <v>4</v>
       </c>
@@ -5588,7 +5592,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12">
         <v>5</v>
       </c>
@@ -5626,7 +5630,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12">
         <v>6</v>
       </c>
@@ -5664,7 +5668,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12">
         <v>7</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12">
         <v>8</v>
       </c>
@@ -5740,7 +5744,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12">
         <v>9</v>
       </c>
@@ -5778,7 +5782,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12">
         <v>10</v>
       </c>
@@ -5816,7 +5820,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12">
         <v>11</v>
       </c>
@@ -5854,7 +5858,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12">
         <v>12</v>
       </c>
@@ -5892,7 +5896,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12">
         <v>13</v>
       </c>
@@ -5930,7 +5934,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12">
         <v>14</v>
       </c>
@@ -5968,7 +5972,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12">
         <v>15</v>
       </c>
@@ -6006,7 +6010,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12">
         <v>16</v>
       </c>
@@ -6044,7 +6048,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12">
         <v>17</v>
       </c>
@@ -6082,7 +6086,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12">
         <v>18</v>
       </c>
@@ -6120,7 +6124,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12">
         <v>19</v>
       </c>
@@ -6158,7 +6162,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12">
         <v>1</v>
       </c>
@@ -6196,7 +6200,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12">
         <v>2</v>
       </c>
@@ -6234,7 +6238,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12">
         <v>3</v>
       </c>
@@ -6272,7 +6276,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12">
         <v>4</v>
       </c>
@@ -6310,7 +6314,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12">
         <v>5</v>
       </c>
@@ -6348,7 +6352,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12">
         <v>6</v>
       </c>
@@ -6386,7 +6390,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12">
         <v>7</v>
       </c>
@@ -6424,7 +6428,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12">
         <v>1</v>
       </c>
@@ -6462,7 +6466,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12">
         <v>2</v>
       </c>
@@ -6500,7 +6504,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12">
         <v>3</v>
       </c>
@@ -6538,7 +6542,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12">
         <v>4</v>
       </c>
@@ -6576,7 +6580,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12">
         <v>1</v>
       </c>
@@ -6614,7 +6618,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12">
         <v>2</v>
       </c>
@@ -6652,7 +6656,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12">
         <v>3</v>
       </c>
@@ -6690,7 +6694,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12">
         <v>1</v>
       </c>
@@ -6728,7 +6732,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12">
         <v>2</v>
       </c>
@@ -6766,7 +6770,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12">
         <v>3</v>
       </c>
@@ -6804,7 +6808,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12">
         <v>4</v>
       </c>
@@ -6842,7 +6846,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12">
         <v>5</v>
       </c>
@@ -6880,7 +6884,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12">
         <v>6</v>
       </c>
@@ -6918,7 +6922,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12">
         <v>1</v>
       </c>
@@ -6956,7 +6960,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12">
         <v>2</v>
       </c>
@@ -6994,7 +6998,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12">
         <v>3</v>
       </c>
@@ -7032,7 +7036,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12">
         <v>4</v>
       </c>
@@ -7070,7 +7074,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12">
         <v>5</v>
       </c>
@@ -7108,7 +7112,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12">
         <v>6</v>
       </c>
@@ -7146,7 +7150,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12">
         <v>7</v>
       </c>
@@ -7184,7 +7188,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12">
         <v>8</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12">
         <v>9</v>
       </c>
@@ -7260,7 +7264,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12">
         <v>10</v>
       </c>
@@ -7298,7 +7302,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12">
         <v>11</v>
       </c>
@@ -7336,7 +7340,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="12">
         <v>12</v>
       </c>
@@ -7374,7 +7378,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12">
         <v>13</v>
       </c>
@@ -7412,7 +7416,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12">
         <v>14</v>
       </c>
@@ -7450,7 +7454,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12">
         <v>15</v>
       </c>
@@ -7488,7 +7492,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="12">
         <v>16</v>
       </c>
@@ -7526,7 +7530,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12">
         <v>17</v>
       </c>
@@ -7564,7 +7568,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12">
         <v>18</v>
       </c>
@@ -7602,7 +7606,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12">
         <v>19</v>
       </c>
@@ -7640,7 +7644,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12">
         <v>20</v>
       </c>
@@ -7678,7 +7682,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12">
         <v>21</v>
       </c>
@@ -7716,7 +7720,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="12">
         <v>22</v>
       </c>
@@ -7754,7 +7758,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12">
         <v>23</v>
       </c>
@@ -7792,7 +7796,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12">
         <v>24</v>
       </c>
@@ -7830,7 +7834,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12">
         <v>25</v>
       </c>
@@ -7868,7 +7872,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="12">
         <v>26</v>
       </c>
@@ -7906,7 +7910,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12">
         <v>27</v>
       </c>
@@ -7944,7 +7948,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="12">
         <v>28</v>
       </c>
@@ -7982,7 +7986,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12">
         <v>29</v>
       </c>
@@ -8020,7 +8024,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="12">
         <v>30</v>
       </c>
@@ -8058,7 +8062,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <v>31</v>
       </c>
@@ -8096,7 +8100,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="12">
         <v>1</v>
       </c>
@@ -8134,7 +8138,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12">
         <v>2</v>
       </c>
@@ -8172,7 +8176,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="12">
         <v>3</v>
       </c>
@@ -8210,7 +8214,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12">
         <v>4</v>
       </c>
@@ -8248,7 +8252,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="12">
         <v>5</v>
       </c>
@@ -8286,7 +8290,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12">
         <v>6</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="12">
         <v>7</v>
       </c>
@@ -8362,7 +8366,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12">
         <v>1</v>
       </c>
@@ -8400,7 +8404,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>2</v>
       </c>
@@ -8438,7 +8442,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12">
         <v>3</v>
       </c>
@@ -8476,7 +8480,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="12">
         <v>1</v>
       </c>
@@ -8514,7 +8518,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12">
         <v>1</v>
       </c>
@@ -8552,7 +8556,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="12">
         <v>2</v>
       </c>
@@ -8590,7 +8594,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12">
         <v>3</v>
       </c>
@@ -8628,7 +8632,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="12">
         <v>4</v>
       </c>
@@ -8666,7 +8670,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12">
         <v>5</v>
       </c>
@@ -8704,7 +8708,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="12">
         <v>6</v>
       </c>
@@ -8742,7 +8746,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12">
         <v>7</v>
       </c>
@@ -8780,7 +8784,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="12">
         <v>8</v>
       </c>
@@ -8818,7 +8822,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12">
         <v>9</v>
       </c>
@@ -8856,7 +8860,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="12">
         <v>10</v>
       </c>
@@ -8894,7 +8898,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12">
         <v>11</v>
       </c>
@@ -8932,7 +8936,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="12">
         <v>12</v>
       </c>
@@ -8970,7 +8974,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12">
         <v>13</v>
       </c>
@@ -9008,7 +9012,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="12">
         <v>14</v>
       </c>
@@ -9046,7 +9050,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12">
         <v>15</v>
       </c>
@@ -9084,7 +9088,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="12">
         <v>16</v>
       </c>
@@ -9122,7 +9126,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12">
         <v>17</v>
       </c>
@@ -9160,7 +9164,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="12">
         <v>18</v>
       </c>
@@ -9198,7 +9202,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12">
         <v>19</v>
       </c>
@@ -9236,7 +9240,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12">
         <v>20</v>
       </c>
@@ -9274,7 +9278,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12">
         <v>21</v>
       </c>
@@ -9312,7 +9316,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12">
         <v>22</v>
       </c>
@@ -9350,7 +9354,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12">
         <v>23</v>
       </c>
@@ -9388,7 +9392,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12">
         <v>24</v>
       </c>
@@ -9426,7 +9430,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12">
         <v>25</v>
       </c>
@@ -9464,7 +9468,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="12">
         <v>26</v>
       </c>
@@ -9502,7 +9506,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12">
         <v>27</v>
       </c>
@@ -9540,7 +9544,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12">
         <v>28</v>
       </c>
@@ -9578,7 +9582,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12">
         <v>29</v>
       </c>
@@ -9616,7 +9620,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12">
         <v>1</v>
       </c>
@@ -9654,7 +9658,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12">
         <v>2</v>
       </c>
@@ -9692,7 +9696,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="12">
         <v>3</v>
       </c>
@@ -9730,7 +9734,7 @@
         <v>44518</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12">
         <v>1</v>
       </c>
@@ -9768,7 +9772,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12">
         <v>2</v>
       </c>
@@ -9806,7 +9810,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12">
         <v>3</v>
       </c>
@@ -9844,7 +9848,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12">
         <v>1</v>
       </c>
@@ -9882,7 +9886,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12">
         <v>2</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12">
         <v>1</v>
       </c>
@@ -9958,7 +9962,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12">
         <v>2</v>
       </c>
@@ -9996,7 +10000,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12">
         <v>3</v>
       </c>
@@ -10034,7 +10038,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12">
         <v>4</v>
       </c>
@@ -10072,7 +10076,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="12">
         <v>5</v>
       </c>
@@ -10110,7 +10114,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12">
         <v>6</v>
       </c>
@@ -10148,7 +10152,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12">
         <v>7</v>
       </c>
@@ -10186,7 +10190,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12">
         <v>8</v>
       </c>
@@ -10224,7 +10228,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12">
         <v>9</v>
       </c>
@@ -10262,7 +10266,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12">
         <v>10</v>
       </c>
@@ -10300,7 +10304,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="12">
         <v>11</v>
       </c>
@@ -10338,7 +10342,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12">
         <v>12</v>
       </c>
@@ -10376,7 +10380,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12">
         <v>13</v>
       </c>
@@ -10414,7 +10418,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12">
         <v>1</v>
       </c>
@@ -10452,7 +10456,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12">
         <v>2</v>
       </c>
@@ -10490,7 +10494,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12">
         <v>3</v>
       </c>
@@ -10528,7 +10532,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12">
         <v>4</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12">
         <v>5</v>
       </c>
@@ -10604,7 +10608,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12">
         <v>6</v>
       </c>
@@ -10642,7 +10646,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12">
         <v>7</v>
       </c>
@@ -10680,7 +10684,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12">
         <v>8</v>
       </c>
@@ -10718,7 +10722,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12">
         <v>9</v>
       </c>
@@ -10756,7 +10760,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="12">
         <v>10</v>
       </c>
@@ -10794,7 +10798,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12">
         <v>11</v>
       </c>
@@ -10832,7 +10836,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="12">
         <v>12</v>
       </c>
@@ -10870,7 +10874,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12">
         <v>13</v>
       </c>
@@ -10908,7 +10912,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12">
         <v>14</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12">
         <v>15</v>
       </c>
@@ -10984,7 +10988,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12">
         <v>16</v>
       </c>
@@ -11022,7 +11026,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12">
         <v>17</v>
       </c>
@@ -11060,7 +11064,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="12">
         <v>18</v>
       </c>
@@ -11098,7 +11102,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12">
         <v>19</v>
       </c>
@@ -11136,7 +11140,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12">
         <v>20</v>
       </c>
@@ -11174,7 +11178,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12">
         <v>21</v>
       </c>
@@ -11212,7 +11216,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12">
         <v>22</v>
       </c>
@@ -11250,7 +11254,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12">
         <v>23</v>
       </c>
@@ -11288,7 +11292,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12">
         <v>24</v>
       </c>
@@ -11326,7 +11330,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12">
         <v>25</v>
       </c>
@@ -11364,7 +11368,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="12">
         <v>26</v>
       </c>
@@ -11402,7 +11406,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12">
         <v>27</v>
       </c>
@@ -11440,7 +11444,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="12">
         <v>28</v>
       </c>
@@ -11478,7 +11482,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12">
         <v>29</v>
       </c>
@@ -11516,7 +11520,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="12">
         <v>30</v>
       </c>
@@ -11554,7 +11558,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12">
         <v>31</v>
       </c>
@@ -11592,7 +11596,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="12">
         <v>32</v>
       </c>
@@ -11630,7 +11634,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12">
         <v>33</v>
       </c>
@@ -11668,7 +11672,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="12">
         <v>34</v>
       </c>
@@ -11706,7 +11710,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12">
         <v>35</v>
       </c>
@@ -11744,7 +11748,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12">
         <v>36</v>
       </c>
@@ -11782,7 +11786,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12">
         <v>37</v>
       </c>
@@ -11820,7 +11824,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="12">
         <v>38</v>
       </c>
@@ -11858,7 +11862,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12">
         <v>39</v>
       </c>
@@ -11896,7 +11900,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12">
         <v>40</v>
       </c>
@@ -11934,7 +11938,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="12">
         <v>41</v>
       </c>
@@ -11972,7 +11976,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="12">
         <v>42</v>
       </c>
@@ -12010,7 +12014,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="12">
         <v>43</v>
       </c>
@@ -12048,7 +12052,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12">
         <v>44</v>
       </c>
@@ -12086,7 +12090,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12">
         <v>45</v>
       </c>
@@ -12124,7 +12128,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12">
         <v>46</v>
       </c>
@@ -12162,7 +12166,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12">
         <v>47</v>
       </c>
@@ -12200,7 +12204,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12">
         <v>48</v>
       </c>
@@ -12238,7 +12242,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="12">
         <v>49</v>
       </c>
@@ -12276,7 +12280,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12">
         <v>50</v>
       </c>
@@ -12314,7 +12318,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="12">
         <v>1</v>
       </c>
@@ -12352,7 +12356,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12">
         <v>2</v>
       </c>
@@ -12390,7 +12394,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="12">
         <v>3</v>
       </c>
@@ -12428,7 +12432,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="12">
         <v>4</v>
       </c>
@@ -12466,7 +12470,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="12">
         <v>5</v>
       </c>
@@ -12504,7 +12508,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="12">
         <v>6</v>
       </c>
@@ -12542,7 +12546,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="12">
         <v>7</v>
       </c>
@@ -12580,7 +12584,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="12">
         <v>1</v>
       </c>
@@ -12618,7 +12622,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="12">
         <v>2</v>
       </c>
@@ -12656,7 +12660,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="12">
         <v>3</v>
       </c>
@@ -12694,7 +12698,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="12">
         <v>4</v>
       </c>
@@ -12732,7 +12736,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="12">
         <v>5</v>
       </c>
@@ -12770,7 +12774,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="12">
         <v>6</v>
       </c>
@@ -12808,7 +12812,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="12">
         <v>7</v>
       </c>
@@ -12846,7 +12850,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="12">
         <v>1</v>
       </c>
@@ -12884,7 +12888,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="12">
         <v>2</v>
       </c>
@@ -12922,7 +12926,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="12">
         <v>1</v>
       </c>
@@ -12960,7 +12964,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="12">
         <v>2</v>
       </c>
@@ -12998,7 +13002,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="12">
         <v>1</v>
       </c>
@@ -13036,7 +13040,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="12">
         <v>2</v>
       </c>
@@ -13074,7 +13078,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="12">
         <v>1</v>
       </c>
@@ -13112,7 +13116,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="12">
         <v>2</v>
       </c>
@@ -13150,7 +13154,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="12">
         <v>3</v>
       </c>
@@ -13188,7 +13192,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="12">
         <v>4</v>
       </c>
@@ -13226,7 +13230,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="12">
         <v>5</v>
       </c>
@@ -13264,7 +13268,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="12">
         <v>6</v>
       </c>
@@ -13302,7 +13306,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="12">
         <v>7</v>
       </c>
@@ -13340,7 +13344,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="12">
         <v>8</v>
       </c>
@@ -13378,7 +13382,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="12">
         <v>1</v>
       </c>
@@ -13416,7 +13420,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12">
         <v>2</v>
       </c>
@@ -13454,7 +13458,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="12">
         <v>3</v>
       </c>
@@ -13492,7 +13496,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="12">
         <v>4</v>
       </c>
@@ -13530,7 +13534,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="12">
         <v>5</v>
       </c>
@@ -13568,7 +13572,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="12">
         <v>6</v>
       </c>
@@ -13606,7 +13610,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="12">
         <v>7</v>
       </c>
@@ -13644,7 +13648,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="12">
         <v>8</v>
       </c>
@@ -13682,7 +13686,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="12">
         <v>9</v>
       </c>
@@ -13720,7 +13724,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="12">
         <v>10</v>
       </c>
@@ -13758,7 +13762,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="12">
         <v>11</v>
       </c>
@@ -13796,7 +13800,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12">
         <v>12</v>
       </c>
@@ -13834,7 +13838,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="12">
         <v>13</v>
       </c>
@@ -13872,7 +13876,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12">
         <v>14</v>
       </c>
@@ -13910,7 +13914,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="12">
         <v>15</v>
       </c>
@@ -13948,7 +13952,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="12">
         <v>16</v>
       </c>
@@ -13986,7 +13990,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="12">
         <v>17</v>
       </c>
@@ -14024,7 +14028,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="12">
         <v>18</v>
       </c>
@@ -14062,7 +14066,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="12">
         <v>19</v>
       </c>
@@ -14100,7 +14104,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="12">
         <v>20</v>
       </c>
@@ -14138,7 +14142,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="12">
         <v>21</v>
       </c>
@@ -14176,7 +14180,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="12">
         <v>22</v>
       </c>
@@ -14214,7 +14218,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="12">
         <v>23</v>
       </c>
@@ -14252,7 +14256,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="12">
         <v>24</v>
       </c>
@@ -14290,7 +14294,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="12">
         <v>25</v>
       </c>
@@ -14328,7 +14332,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="12">
         <v>26</v>
       </c>
@@ -14366,7 +14370,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="12">
         <v>27</v>
       </c>
@@ -14404,7 +14408,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="12">
         <v>28</v>
       </c>
@@ -14442,7 +14446,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="12">
         <v>1</v>
       </c>
@@ -14480,7 +14484,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="12">
         <v>2</v>
       </c>
@@ -14518,7 +14522,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="12">
         <v>3</v>
       </c>
@@ -14556,7 +14560,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="12">
         <v>4</v>
       </c>
@@ -14594,7 +14598,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="12">
         <v>5</v>
       </c>
@@ -14632,7 +14636,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="12">
         <v>6</v>
       </c>
@@ -14670,7 +14674,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="12">
         <v>7</v>
       </c>
@@ -14708,7 +14712,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="12">
         <v>8</v>
       </c>
@@ -14746,7 +14750,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="12">
         <v>9</v>
       </c>
@@ -14784,7 +14788,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="12">
         <v>10</v>
       </c>
@@ -14933,7 +14937,7 @@
         <v>19</v>
       </c>
       <c r="L380" s="11">
-        <v>44315</v>
+        <v>44287</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
@@ -19382,7 +19386,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="12">
         <v>1</v>
       </c>
@@ -19420,7 +19424,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="12">
         <v>2</v>
       </c>
@@ -19458,7 +19462,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="12">
         <v>3</v>
       </c>
@@ -19496,7 +19500,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="12">
         <v>1</v>
       </c>
@@ -19534,7 +19538,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="12">
         <v>1</v>
       </c>
@@ -19572,7 +19576,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="12">
         <v>2</v>
       </c>
@@ -19610,7 +19614,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="12">
         <v>3</v>
       </c>
@@ -19648,7 +19652,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="12">
         <v>4</v>
       </c>
@@ -19686,7 +19690,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="12">
         <v>5</v>
       </c>
@@ -19724,7 +19728,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="12">
         <v>6</v>
       </c>
@@ -19762,7 +19766,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="12">
         <v>1</v>
       </c>
@@ -19800,7 +19804,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="12">
         <v>2</v>
       </c>
@@ -19838,7 +19842,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="12">
         <v>3</v>
       </c>
@@ -19876,7 +19880,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="12">
         <v>4</v>
       </c>
@@ -19914,7 +19918,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="12">
         <v>5</v>
       </c>
@@ -19952,7 +19956,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="12">
         <v>6</v>
       </c>
@@ -19990,7 +19994,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="12">
         <v>1</v>
       </c>
@@ -20028,7 +20032,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="12">
         <v>2</v>
       </c>
@@ -20066,7 +20070,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="12">
         <v>1</v>
       </c>
@@ -20104,7 +20108,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="12">
         <v>2</v>
       </c>
@@ -20142,7 +20146,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="12">
         <v>3</v>
       </c>
@@ -20180,7 +20184,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="12">
         <v>1</v>
       </c>
@@ -20218,7 +20222,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="12">
         <v>2</v>
       </c>
@@ -20256,7 +20260,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="12">
         <v>3</v>
       </c>
@@ -20294,7 +20298,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="12">
         <v>4</v>
       </c>
@@ -20332,7 +20336,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="12">
         <v>5</v>
       </c>
@@ -20370,7 +20374,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="12">
         <v>6</v>
       </c>
@@ -20408,7 +20412,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="12">
         <v>7</v>
       </c>
@@ -20446,7 +20450,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="12">
         <v>8</v>
       </c>
@@ -20484,7 +20488,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="12">
         <v>9</v>
       </c>
@@ -20522,7 +20526,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="12">
         <v>10</v>
       </c>
@@ -20560,7 +20564,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="12">
         <v>11</v>
       </c>
@@ -20598,7 +20602,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="12">
         <v>12</v>
       </c>
@@ -20636,7 +20640,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="12">
         <v>13</v>
       </c>
@@ -20674,7 +20678,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="12">
         <v>14</v>
       </c>
@@ -20712,7 +20716,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="12">
         <v>15</v>
       </c>
@@ -20750,7 +20754,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12">
         <v>16</v>
       </c>
@@ -20788,7 +20792,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12">
         <v>17</v>
       </c>
@@ -20826,7 +20830,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12">
         <v>18</v>
       </c>
@@ -20864,7 +20868,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12">
         <v>19</v>
       </c>
@@ -20902,7 +20906,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12">
         <v>20</v>
       </c>
@@ -20940,7 +20944,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12">
         <v>21</v>
       </c>
@@ -20978,7 +20982,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12">
         <v>22</v>
       </c>
@@ -21016,7 +21020,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12">
         <v>23</v>
       </c>
@@ -21054,7 +21058,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12">
         <v>24</v>
       </c>
@@ -21092,7 +21096,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12">
         <v>25</v>
       </c>
@@ -21130,7 +21134,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12">
         <v>26</v>
       </c>
@@ -21168,7 +21172,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12">
         <v>27</v>
       </c>
@@ -21206,7 +21210,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12">
         <v>28</v>
       </c>
@@ -21244,7 +21248,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12">
         <v>29</v>
       </c>
@@ -21282,7 +21286,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12">
         <v>30</v>
       </c>
@@ -21320,7 +21324,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12">
         <v>31</v>
       </c>
@@ -21358,7 +21362,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12">
         <v>32</v>
       </c>
@@ -21396,7 +21400,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12">
         <v>33</v>
       </c>
@@ -21434,7 +21438,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12">
         <v>34</v>
       </c>
@@ -21472,7 +21476,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12">
         <v>35</v>
       </c>
@@ -21510,7 +21514,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12">
         <v>36</v>
       </c>
@@ -21548,7 +21552,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12">
         <v>37</v>
       </c>
@@ -21586,7 +21590,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12">
         <v>38</v>
       </c>
@@ -21624,7 +21628,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12">
         <v>39</v>
       </c>
@@ -21662,7 +21666,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12">
         <v>40</v>
       </c>
@@ -21700,7 +21704,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12">
         <v>1</v>
       </c>
@@ -21738,7 +21742,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12">
         <v>2</v>
       </c>
@@ -21776,7 +21780,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12">
         <v>3</v>
       </c>
@@ -21814,7 +21818,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12">
         <v>4</v>
       </c>
@@ -21852,7 +21856,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12">
         <v>1</v>
       </c>
@@ -21890,7 +21894,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12">
         <v>2</v>
       </c>
@@ -21928,7 +21932,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12">
         <v>3</v>
       </c>
@@ -21966,7 +21970,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12">
         <v>4</v>
       </c>
@@ -22004,7 +22008,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12">
         <v>5</v>
       </c>
@@ -22042,7 +22046,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12">
         <v>6</v>
       </c>
@@ -22080,7 +22084,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12">
         <v>7</v>
       </c>
@@ -22118,7 +22122,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12">
         <v>8</v>
       </c>
@@ -22156,7 +22160,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12">
         <v>9</v>
       </c>
@@ -22194,7 +22198,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12">
         <v>10</v>
       </c>
@@ -22232,7 +22236,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12">
         <v>1</v>
       </c>
@@ -22270,7 +22274,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12">
         <v>2</v>
       </c>
@@ -22308,7 +22312,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12">
         <v>3</v>
       </c>
@@ -22346,7 +22350,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12">
         <v>4</v>
       </c>
@@ -22384,7 +22388,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12">
         <v>5</v>
       </c>
@@ -22422,7 +22426,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12">
         <v>6</v>
       </c>
@@ -22460,7 +22464,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12">
         <v>7</v>
       </c>
@@ -22498,7 +22502,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12">
         <v>8</v>
       </c>
@@ -22536,7 +22540,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12">
         <v>9</v>
       </c>
@@ -22574,7 +22578,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12">
         <v>10</v>
       </c>
@@ -22612,7 +22616,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12">
         <v>11</v>
       </c>
@@ -22650,7 +22654,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12">
         <v>12</v>
       </c>
@@ -22688,7 +22692,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12">
         <v>13</v>
       </c>
@@ -22726,7 +22730,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12">
         <v>14</v>
       </c>
@@ -22764,7 +22768,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12">
         <v>15</v>
       </c>
@@ -22802,7 +22806,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12">
         <v>16</v>
       </c>
@@ -22840,7 +22844,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12">
         <v>17</v>
       </c>
@@ -22878,7 +22882,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12">
         <v>18</v>
       </c>
@@ -22916,7 +22920,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12">
         <v>19</v>
       </c>
@@ -22954,7 +22958,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12">
         <v>20</v>
       </c>
@@ -22992,7 +22996,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="12">
         <v>1</v>
       </c>
@@ -23030,7 +23034,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="12">
         <v>2</v>
       </c>
@@ -23068,7 +23072,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="12">
         <v>3</v>
       </c>
@@ -23106,7 +23110,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="12">
         <v>1</v>
       </c>
@@ -23144,7 +23148,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="12">
         <v>2</v>
       </c>
@@ -23182,7 +23186,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="12">
         <v>1</v>
       </c>
@@ -23220,7 +23224,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="12">
         <v>2</v>
       </c>
@@ -23258,7 +23262,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="12">
         <v>1</v>
       </c>
@@ -23296,7 +23300,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="12">
         <v>2</v>
       </c>
@@ -23334,7 +23338,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="12">
         <v>3</v>
       </c>
@@ -23372,7 +23376,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="12">
         <v>1</v>
       </c>
@@ -23410,7 +23414,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="12">
         <v>2</v>
       </c>
@@ -23448,7 +23452,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="12">
         <v>3</v>
       </c>
@@ -23486,7 +23490,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="12">
         <v>4</v>
       </c>
@@ -23524,7 +23528,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="12">
         <v>5</v>
       </c>
@@ -23562,7 +23566,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="12">
         <v>6</v>
       </c>
@@ -23600,7 +23604,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="12">
         <v>7</v>
       </c>
@@ -23638,7 +23642,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="12">
         <v>8</v>
       </c>
@@ -23676,7 +23680,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="12">
         <v>9</v>
       </c>
@@ -23714,7 +23718,7 @@
         <v>44483</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="12">
         <v>1</v>
       </c>
@@ -23752,7 +23756,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="12">
         <v>2</v>
       </c>
@@ -23790,7 +23794,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="12">
         <v>3</v>
       </c>
@@ -23828,7 +23832,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="12">
         <v>4</v>
       </c>
@@ -23866,7 +23870,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="12">
         <v>5</v>
       </c>
@@ -23904,7 +23908,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="12">
         <v>6</v>
       </c>
@@ -23942,7 +23946,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="12">
         <v>7</v>
       </c>
@@ -23980,7 +23984,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="12">
         <v>8</v>
       </c>
@@ -24018,7 +24022,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="12">
         <v>9</v>
       </c>
@@ -24056,7 +24060,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="12">
         <v>10</v>
       </c>
@@ -24094,7 +24098,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="12">
         <v>11</v>
       </c>
@@ -24132,7 +24136,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="12">
         <v>12</v>
       </c>
@@ -24170,7 +24174,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="12">
         <v>13</v>
       </c>
@@ -24208,7 +24212,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="12">
         <v>1</v>
       </c>
@@ -24246,7 +24250,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="12">
         <v>2</v>
       </c>
@@ -24284,7 +24288,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="12">
         <v>1</v>
       </c>
@@ -24322,7 +24326,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="12">
         <v>2</v>
       </c>
@@ -24360,7 +24364,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="12">
         <v>3</v>
       </c>
@@ -24398,7 +24402,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="12">
         <v>1</v>
       </c>
@@ -24436,7 +24440,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="12">
         <v>1</v>
       </c>
@@ -24474,7 +24478,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="12">
         <v>2</v>
       </c>
@@ -24512,7 +24516,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="12">
         <v>3</v>
       </c>
@@ -24550,7 +24554,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="12">
         <v>1</v>
       </c>
@@ -24588,7 +24592,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="12">
         <v>2</v>
       </c>
@@ -24626,7 +24630,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="12">
         <v>3</v>
       </c>
@@ -24664,7 +24668,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="12">
         <v>4</v>
       </c>
@@ -24702,7 +24706,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="12">
         <v>5</v>
       </c>
@@ -24740,7 +24744,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="12">
         <v>6</v>
       </c>
@@ -24778,7 +24782,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="12">
         <v>7</v>
       </c>
@@ -24816,7 +24820,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="12">
         <v>8</v>
       </c>
@@ -24854,7 +24858,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="12">
         <v>9</v>
       </c>
@@ -24892,7 +24896,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="12">
         <v>10</v>
       </c>
@@ -24930,7 +24934,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="12">
         <v>11</v>
       </c>
@@ -24968,7 +24972,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="12">
         <v>12</v>
       </c>
@@ -25006,7 +25010,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="12">
         <v>13</v>
       </c>
@@ -25044,7 +25048,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="12">
         <v>14</v>
       </c>
@@ -25082,7 +25086,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="12">
         <v>15</v>
       </c>
@@ -25120,7 +25124,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="12">
         <v>16</v>
       </c>
@@ -25158,7 +25162,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="12">
         <v>17</v>
       </c>
@@ -25196,7 +25200,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="12">
         <v>18</v>
       </c>
@@ -25234,7 +25238,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="12">
         <v>19</v>
       </c>
@@ -25272,7 +25276,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="12">
         <v>20</v>
       </c>
@@ -25310,7 +25314,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="12">
         <v>21</v>
       </c>
@@ -25348,7 +25352,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="12">
         <v>22</v>
       </c>
@@ -25386,7 +25390,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="12">
         <v>23</v>
       </c>
@@ -25424,7 +25428,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="12">
         <v>24</v>
       </c>
@@ -25462,7 +25466,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="12">
         <v>25</v>
       </c>
@@ -25500,7 +25504,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="12">
         <v>26</v>
       </c>
@@ -25538,7 +25542,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="12">
         <v>27</v>
       </c>
@@ -25576,7 +25580,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="12">
         <v>28</v>
       </c>
@@ -25614,7 +25618,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="12">
         <v>29</v>
       </c>
@@ -25652,7 +25656,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="12">
         <v>30</v>
       </c>
@@ -25690,7 +25694,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="12">
         <v>1</v>
       </c>
@@ -25728,7 +25732,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="12">
         <v>2</v>
       </c>
@@ -25766,7 +25770,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="12">
         <v>3</v>
       </c>
@@ -25804,7 +25808,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="12">
         <v>4</v>
       </c>
@@ -25842,7 +25846,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="12">
         <v>1</v>
       </c>
@@ -25880,7 +25884,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="12">
         <v>2</v>
       </c>
@@ -25918,7 +25922,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="12">
         <v>1</v>
       </c>
@@ -25956,7 +25960,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="12">
         <v>2</v>
       </c>
@@ -25994,7 +25998,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="12">
         <v>3</v>
       </c>
@@ -26032,7 +26036,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="12">
         <v>4</v>
       </c>
@@ -26070,7 +26074,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="12">
         <v>5</v>
       </c>
@@ -26108,7 +26112,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="12">
         <v>1</v>
       </c>
@@ -26146,7 +26150,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="12">
         <v>2</v>
       </c>
@@ -26184,7 +26188,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="12">
         <v>1</v>
       </c>
@@ -26222,7 +26226,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="12">
         <v>2</v>
       </c>
@@ -26260,7 +26264,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="12">
         <v>3</v>
       </c>
@@ -26298,7 +26302,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="12">
         <v>4</v>
       </c>
@@ -26336,7 +26340,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="12">
         <v>5</v>
       </c>
@@ -26374,7 +26378,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="12">
         <v>6</v>
       </c>
@@ -26412,7 +26416,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="12">
         <v>7</v>
       </c>
@@ -26450,7 +26454,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="12">
         <v>8</v>
       </c>
@@ -26488,7 +26492,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="12">
         <v>9</v>
       </c>
@@ -26526,7 +26530,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="12">
         <v>10</v>
       </c>
@@ -26564,7 +26568,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="12">
         <v>11</v>
       </c>
@@ -26602,7 +26606,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="12">
         <v>12</v>
       </c>
@@ -26640,7 +26644,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="12">
         <v>1</v>
       </c>
@@ -26678,7 +26682,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="12">
         <v>2</v>
       </c>
@@ -26716,7 +26720,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="12">
         <v>1</v>
       </c>
@@ -26754,7 +26758,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="12">
         <v>2</v>
       </c>
@@ -26792,7 +26796,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="12">
         <v>3</v>
       </c>
@@ -26830,7 +26834,7 @@
         <v>44315</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="12">
         <v>1</v>
       </c>
@@ -26868,7 +26872,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="12">
         <v>2</v>
       </c>
@@ -26906,7 +26910,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="12">
         <v>3</v>
       </c>
@@ -26944,7 +26948,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="12">
         <v>1</v>
       </c>
@@ -26982,7 +26986,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="12">
         <v>2</v>
       </c>
@@ -27020,7 +27024,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="12">
         <v>3</v>
       </c>
@@ -27058,7 +27062,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="12">
         <v>4</v>
       </c>
@@ -27096,7 +27100,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="12">
         <v>5</v>
       </c>
@@ -27134,7 +27138,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="12">
         <v>6</v>
       </c>
@@ -27172,7 +27176,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="12">
         <v>7</v>
       </c>
@@ -27210,7 +27214,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="12">
         <v>8</v>
       </c>
@@ -27248,7 +27252,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="12">
         <v>9</v>
       </c>
@@ -27286,7 +27290,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="12">
         <v>10</v>
       </c>
@@ -27324,7 +27328,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="12">
         <v>11</v>
       </c>
@@ -27362,7 +27366,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="12">
         <v>12</v>
       </c>
@@ -27400,7 +27404,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="12">
         <v>13</v>
       </c>
@@ -27438,7 +27442,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="12">
         <v>14</v>
       </c>
@@ -27476,7 +27480,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="12">
         <v>15</v>
       </c>
@@ -27514,7 +27518,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="12">
         <v>16</v>
       </c>
@@ -27552,7 +27556,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="12">
         <v>17</v>
       </c>
@@ -27590,7 +27594,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="12">
         <v>18</v>
       </c>
@@ -27628,7 +27632,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="12">
         <v>19</v>
       </c>
@@ -27666,7 +27670,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="12">
         <v>20</v>
       </c>
@@ -27704,7 +27708,7 @@
         <v>44357</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="12">
         <v>1</v>
       </c>
@@ -27742,7 +27746,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="12">
         <v>2</v>
       </c>
@@ -27780,7 +27784,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="12">
         <v>3</v>
       </c>
@@ -27818,7 +27822,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="12">
         <v>4</v>
       </c>
@@ -27856,7 +27860,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" s="12">
         <v>5</v>
       </c>
@@ -27894,7 +27898,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="12">
         <v>6</v>
       </c>
@@ -27932,7 +27936,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="12">
         <v>7</v>
       </c>
@@ -27970,7 +27974,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="12">
         <v>8</v>
       </c>
@@ -28008,7 +28012,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="12">
         <v>9</v>
       </c>
@@ -28046,7 +28050,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="12">
         <v>10</v>
       </c>
@@ -28084,7 +28088,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="12">
         <v>11</v>
       </c>
@@ -28122,7 +28126,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="12">
         <v>12</v>
       </c>
@@ -28160,7 +28164,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="12">
         <v>13</v>
       </c>
@@ -28198,7 +28202,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="12">
         <v>14</v>
       </c>
@@ -28236,7 +28240,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="12">
         <v>15</v>
       </c>
@@ -28274,7 +28278,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="12">
         <v>16</v>
       </c>
@@ -28312,7 +28316,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="12">
         <v>17</v>
       </c>
@@ -28350,7 +28354,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="12">
         <v>18</v>
       </c>
@@ -28388,7 +28392,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="12">
         <v>1</v>
       </c>
@@ -28426,7 +28430,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="12">
         <v>2</v>
       </c>
@@ -28464,7 +28468,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="12">
         <v>3</v>
       </c>
@@ -28502,7 +28506,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="12">
         <v>4</v>
       </c>
@@ -28540,7 +28544,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" s="12">
         <v>5</v>
       </c>
@@ -28578,7 +28582,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="12">
         <v>6</v>
       </c>
@@ -28616,7 +28620,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="12">
         <v>7</v>
       </c>
@@ -28654,7 +28658,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="12">
         <v>8</v>
       </c>
@@ -28692,7 +28696,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="12">
         <v>9</v>
       </c>
@@ -28730,7 +28734,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="12">
         <v>10</v>
       </c>
@@ -28768,7 +28772,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="12">
         <v>11</v>
       </c>
@@ -28806,7 +28810,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="12">
         <v>12</v>
       </c>
@@ -28844,7 +28848,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="12">
         <v>13</v>
       </c>
@@ -28882,7 +28886,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="12">
         <v>14</v>
       </c>
@@ -28920,7 +28924,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="12">
         <v>15</v>
       </c>
@@ -28958,7 +28962,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="12">
         <v>1</v>
       </c>
@@ -28996,7 +29000,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="12">
         <v>2</v>
       </c>
@@ -29034,7 +29038,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="12">
         <v>3</v>
       </c>
@@ -29072,7 +29076,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="12">
         <v>4</v>
       </c>
@@ -29110,7 +29114,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="12">
         <v>5</v>
       </c>
@@ -29148,7 +29152,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="12">
         <v>6</v>
       </c>
@@ -29186,7 +29190,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="12">
         <v>7</v>
       </c>
@@ -29224,7 +29228,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="12">
         <v>8</v>
       </c>
@@ -29262,7 +29266,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="12">
         <v>9</v>
       </c>
@@ -29300,7 +29304,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="12">
         <v>10</v>
       </c>
@@ -29338,7 +29342,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="12">
         <v>11</v>
       </c>
@@ -29376,7 +29380,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="12">
         <v>12</v>
       </c>
@@ -29414,7 +29418,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="12">
         <v>13</v>
       </c>
@@ -29452,7 +29456,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="12">
         <v>14</v>
       </c>
@@ -29490,7 +29494,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="12">
         <v>15</v>
       </c>
@@ -29528,7 +29532,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="12">
         <v>16</v>
       </c>
@@ -29566,7 +29570,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="12">
         <v>17</v>
       </c>
@@ -29604,7 +29608,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="12">
         <v>18</v>
       </c>
@@ -29642,7 +29646,7 @@
         <v>44448</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="12">
         <v>1</v>
       </c>
@@ -29680,7 +29684,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="12">
         <v>2</v>
       </c>
@@ -29718,7 +29722,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="12">
         <v>3</v>
       </c>
@@ -29756,7 +29760,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="12">
         <v>1</v>
       </c>
@@ -29794,7 +29798,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="12">
         <v>2</v>
       </c>
@@ -29832,7 +29836,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="12">
         <v>3</v>
       </c>
@@ -29870,7 +29874,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="12">
         <v>4</v>
       </c>
@@ -29908,7 +29912,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="12">
         <v>5</v>
       </c>
@@ -29946,7 +29950,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="12">
         <v>6</v>
       </c>
@@ -29984,7 +29988,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="12">
         <v>7</v>
       </c>
@@ -30022,7 +30026,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="12">
         <v>8</v>
       </c>
@@ -30060,7 +30064,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="12">
         <v>9</v>
       </c>
@@ -30098,7 +30102,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="12">
         <v>10</v>
       </c>
@@ -30136,7 +30140,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" s="12">
         <v>11</v>
       </c>
@@ -30174,7 +30178,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="12">
         <v>12</v>
       </c>
@@ -30212,7 +30216,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="12">
         <v>13</v>
       </c>
@@ -30250,7 +30254,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="12">
         <v>14</v>
       </c>
@@ -30288,7 +30292,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="12">
         <v>15</v>
       </c>
@@ -30326,7 +30330,7 @@
         <v>44434</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="12">
         <v>1</v>
       </c>
@@ -30364,7 +30368,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" s="12">
         <v>2</v>
       </c>
@@ -30402,7 +30406,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="12">
         <v>3</v>
       </c>
@@ -30440,7 +30444,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="12">
         <v>4</v>
       </c>
@@ -30478,7 +30482,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" s="12">
         <v>5</v>
       </c>
@@ -30516,7 +30520,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="12">
         <v>6</v>
       </c>
@@ -30554,7 +30558,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="12">
         <v>7</v>
       </c>
@@ -30593,6 +30597,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L792" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="19"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
